--- a/media/esclerometria/260104-Tabela_Esclerometria - Hydro SiloV02.xlsx
+++ b/media/esclerometria/260104-Tabela_Esclerometria - Hydro SiloV02.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Drives compartilhados\068-23-HydroSilo-OS13e14\250314-Exec\250815-RelatoriosTecnicos\Ensaios Caracterizacao do concreto\251122-R01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e14ca4ed5cbd9145/myWebSitesVScode/espEngFerrovIntegrPontes/parte01_END_concr/media/esclerometria/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71261F2D-52B9-41E5-AEB8-167B7BC1E272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{9A746B6E-5B14-49D6-94F2-6D86E29A27E7}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9A746B6E-5B14-49D6-94F2-6D86E29A27E7}"/>
   </bookViews>
   <sheets>
     <sheet name="TABELA CARBONATACAO" sheetId="4" r:id="rId1"/>
@@ -2830,49 +2830,19 @@
     <xf numFmtId="166" fontId="11" fillId="12" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2899,10 +2869,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2924,12 +2930,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13998,66 +13998,66 @@
       </c>
     </row>
     <row r="4" spans="4:45" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="239" t="s">
+      <c r="D4" s="252" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="241" t="s">
+      <c r="E4" s="254" t="s">
         <v>110</v>
       </c>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
-      <c r="M4" s="242"/>
-      <c r="N4" s="242"/>
-      <c r="O4" s="242"/>
-      <c r="P4" s="242"/>
-      <c r="Q4" s="242"/>
-      <c r="R4" s="242"/>
-      <c r="S4" s="242"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="241" t="s">
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="M4" s="255"/>
+      <c r="N4" s="255"/>
+      <c r="O4" s="255"/>
+      <c r="P4" s="255"/>
+      <c r="Q4" s="255"/>
+      <c r="R4" s="255"/>
+      <c r="S4" s="255"/>
+      <c r="T4" s="256"/>
+      <c r="U4" s="254" t="s">
         <v>1</v>
       </c>
-      <c r="V4" s="242"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="241" t="s">
+      <c r="V4" s="255"/>
+      <c r="W4" s="256"/>
+      <c r="X4" s="254" t="s">
         <v>2</v>
       </c>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="243"/>
-      <c r="AB4" s="246" t="s">
+      <c r="Y4" s="255"/>
+      <c r="Z4" s="256"/>
+      <c r="AB4" s="259" t="s">
         <v>111</v>
       </c>
-      <c r="AC4" s="247" t="str">
+      <c r="AC4" s="260" t="str">
         <f>D4</f>
         <v>Área de Ensaio</v>
       </c>
-      <c r="AD4" s="249" t="s">
+      <c r="AD4" s="243" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="249" t="s">
+      <c r="AE4" s="243" t="s">
         <v>144</v>
       </c>
-      <c r="AF4" s="251" t="s">
+      <c r="AF4" s="262" t="s">
         <v>264</v>
       </c>
-      <c r="AG4" s="249" t="s">
+      <c r="AG4" s="243" t="s">
         <v>139</v>
       </c>
-      <c r="AH4" s="249" t="s">
+      <c r="AH4" s="243" t="s">
         <v>261</v>
       </c>
-      <c r="AI4" s="249" t="s">
+      <c r="AI4" s="243" t="s">
         <v>262</v>
       </c>
-      <c r="AJ4" s="244" t="s">
+      <c r="AJ4" s="257" t="s">
         <v>263</v>
       </c>
-      <c r="AK4" s="255" t="s">
+      <c r="AK4" s="242" t="s">
         <v>173</v>
       </c>
       <c r="AP4" s="118">
@@ -14077,7 +14077,7 @@
       </c>
     </row>
     <row r="5" spans="4:45" ht="53.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="240"/>
+      <c r="D5" s="253"/>
       <c r="E5" s="57">
         <v>1</v>
       </c>
@@ -14144,16 +14144,16 @@
       <c r="Z5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="AB5" s="246"/>
-      <c r="AC5" s="248"/>
-      <c r="AD5" s="250"/>
-      <c r="AE5" s="250"/>
-      <c r="AF5" s="252"/>
-      <c r="AG5" s="250"/>
-      <c r="AH5" s="250"/>
-      <c r="AI5" s="250"/>
-      <c r="AJ5" s="245"/>
-      <c r="AK5" s="255"/>
+      <c r="AB5" s="259"/>
+      <c r="AC5" s="261"/>
+      <c r="AD5" s="241"/>
+      <c r="AE5" s="241"/>
+      <c r="AF5" s="263"/>
+      <c r="AG5" s="241"/>
+      <c r="AH5" s="241"/>
+      <c r="AI5" s="241"/>
+      <c r="AJ5" s="258"/>
+      <c r="AK5" s="242"/>
       <c r="AM5" t="s">
         <v>166</v>
       </c>
@@ -15868,13 +15868,13 @@
         <f>SUMPRODUCT(INDEX(Curvas!$B$3:$E$5,MATCH(AD18,Curvas!$A$3:$A$5,0),0),CHOOSE({1,2,3,4},AG18^3,AG18^2,AG18,1))</f>
         <v>23.086361101305112</v>
       </c>
-      <c r="AQ18" s="256" t="s">
+      <c r="AQ18" s="244" t="s">
         <v>133</v>
       </c>
-      <c r="AR18" s="257">
+      <c r="AR18" s="245">
         <v>80</v>
       </c>
-      <c r="AS18" s="257">
+      <c r="AS18" s="245">
         <v>80</v>
       </c>
     </row>
@@ -15996,9 +15996,9 @@
         <f>SUMPRODUCT(INDEX(Curvas!$B$3:$E$5,MATCH(AD19,Curvas!$A$3:$A$5,0),0),CHOOSE({1,2,3,4},AG19^3,AG19^2,AG19,1))</f>
         <v>24.13334988029106</v>
       </c>
-      <c r="AQ19" s="256"/>
-      <c r="AR19" s="257"/>
-      <c r="AS19" s="257"/>
+      <c r="AQ19" s="244"/>
+      <c r="AR19" s="245"/>
+      <c r="AS19" s="245"/>
     </row>
     <row r="20" spans="4:57" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D20" s="11" t="s">
@@ -16963,10 +16963,10 @@
         <f t="shared" si="11"/>
         <v>24.238168067321677</v>
       </c>
-      <c r="BD27" s="250" t="s">
+      <c r="BD27" s="241" t="s">
         <v>171</v>
       </c>
-      <c r="BE27" s="250" t="s">
+      <c r="BE27" s="241" t="s">
         <v>157</v>
       </c>
     </row>
@@ -17084,8 +17084,8 @@
         <f t="shared" si="11"/>
         <v>26.571644337294739</v>
       </c>
-      <c r="BD28" s="250"/>
-      <c r="BE28" s="250"/>
+      <c r="BD28" s="241"/>
+      <c r="BE28" s="241"/>
     </row>
     <row r="29" spans="4:57" x14ac:dyDescent="0.3">
       <c r="D29" s="11" t="s">
@@ -17204,7 +17204,7 @@
       <c r="AM29" s="116"/>
       <c r="AN29" s="116"/>
       <c r="AO29" s="116"/>
-      <c r="AP29" s="262"/>
+      <c r="AP29" s="250"/>
       <c r="BD29" s="19"/>
       <c r="BE29" s="19"/>
     </row>
@@ -17325,7 +17325,7 @@
       <c r="AM30" s="116"/>
       <c r="AN30" s="116"/>
       <c r="AO30" s="116"/>
-      <c r="AP30" s="262"/>
+      <c r="AP30" s="250"/>
       <c r="BD30" s="19"/>
       <c r="BE30" s="19"/>
     </row>
@@ -17446,7 +17446,7 @@
       <c r="AM31" s="117"/>
       <c r="AN31" s="117"/>
       <c r="AO31" s="117"/>
-      <c r="AP31" s="263"/>
+      <c r="AP31" s="251"/>
       <c r="BD31" s="19"/>
       <c r="BE31" s="19"/>
     </row>
@@ -17586,10 +17586,10 @@
       <c r="S33" s="34"/>
       <c r="T33" s="34"/>
       <c r="AB33" s="35"/>
-      <c r="AC33" s="258" t="s">
+      <c r="AC33" s="246" t="s">
         <v>265</v>
       </c>
-      <c r="AD33" s="259"/>
+      <c r="AD33" s="247"/>
       <c r="AE33" s="227">
         <f>AVERAGE(AE6:AE32)</f>
         <v>36.246457400624067</v>
@@ -17636,10 +17636,10 @@
       <c r="S34" s="34"/>
       <c r="T34" s="34"/>
       <c r="AB34" s="35"/>
-      <c r="AC34" s="260" t="s">
+      <c r="AC34" s="248" t="s">
         <v>168</v>
       </c>
-      <c r="AD34" s="261"/>
+      <c r="AD34" s="249"/>
       <c r="AE34" s="229">
         <f>MEDIAN(AE6:AE32)</f>
         <v>34.285714285714285</v>
@@ -17675,10 +17675,10 @@
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="21"/>
-      <c r="AC35" s="260" t="s">
+      <c r="AC35" s="248" t="s">
         <v>169</v>
       </c>
-      <c r="AD35" s="261"/>
+      <c r="AD35" s="249"/>
       <c r="AE35" s="229">
         <f>_xlfn.STDEV.S(AE6:AE32)</f>
         <v>5.0648398404086965</v>
@@ -17714,10 +17714,10 @@
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
       <c r="K36" s="21"/>
-      <c r="AC36" s="260" t="s">
+      <c r="AC36" s="248" t="s">
         <v>170</v>
       </c>
-      <c r="AD36" s="261"/>
+      <c r="AD36" s="249"/>
       <c r="AE36" s="231">
         <f>AE35/AE33</f>
         <v>0.13973337544213338</v>
@@ -17753,10 +17753,10 @@
       <c r="I37" s="24"/>
       <c r="J37" s="24"/>
       <c r="K37" s="25"/>
-      <c r="AC37" s="253" t="s">
+      <c r="AC37" s="239" t="s">
         <v>266</v>
       </c>
-      <c r="AD37" s="254"/>
+      <c r="AD37" s="240"/>
       <c r="AE37" s="233">
         <f t="shared" ref="AE37:AH37" si="23">AE33-1.645*AE35</f>
         <v>27.91479586315176</v>
@@ -17956,6 +17956,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:T4"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="AJ4:AJ5"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="AC4:AC5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="AG4:AG5"/>
+    <mergeCell ref="AH4:AH5"/>
+    <mergeCell ref="AD4:AD5"/>
+    <mergeCell ref="AF4:AF5"/>
     <mergeCell ref="AC37:AD37"/>
     <mergeCell ref="BD27:BD28"/>
     <mergeCell ref="BE27:BE28"/>
@@ -17969,18 +17981,6 @@
     <mergeCell ref="AC35:AD35"/>
     <mergeCell ref="AC36:AD36"/>
     <mergeCell ref="AP29:AP31"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:T4"/>
-    <mergeCell ref="U4:W4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="AJ4:AJ5"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="AC4:AC5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="AG4:AG5"/>
-    <mergeCell ref="AH4:AH5"/>
-    <mergeCell ref="AD4:AD5"/>
-    <mergeCell ref="AF4:AF5"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="D33:F33 L34:T34">
@@ -19857,63 +19857,63 @@
       </c>
     </row>
     <row r="4" spans="4:44" ht="16.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D4" s="239" t="s">
+      <c r="D4" s="252" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="241" t="s">
+      <c r="E4" s="254" t="s">
         <v>110</v>
       </c>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
-      <c r="H4" s="242"/>
-      <c r="I4" s="242"/>
-      <c r="J4" s="242"/>
-      <c r="K4" s="242"/>
-      <c r="L4" s="242"/>
-      <c r="M4" s="242"/>
-      <c r="N4" s="242"/>
-      <c r="O4" s="242"/>
-      <c r="P4" s="242"/>
-      <c r="Q4" s="242"/>
-      <c r="R4" s="242"/>
-      <c r="S4" s="242"/>
-      <c r="T4" s="243"/>
-      <c r="U4" s="241" t="s">
+      <c r="F4" s="255"/>
+      <c r="G4" s="255"/>
+      <c r="H4" s="255"/>
+      <c r="I4" s="255"/>
+      <c r="J4" s="255"/>
+      <c r="K4" s="255"/>
+      <c r="L4" s="255"/>
+      <c r="M4" s="255"/>
+      <c r="N4" s="255"/>
+      <c r="O4" s="255"/>
+      <c r="P4" s="255"/>
+      <c r="Q4" s="255"/>
+      <c r="R4" s="255"/>
+      <c r="S4" s="255"/>
+      <c r="T4" s="256"/>
+      <c r="U4" s="254" t="s">
         <v>1</v>
       </c>
-      <c r="V4" s="242"/>
-      <c r="W4" s="243"/>
-      <c r="X4" s="241" t="s">
+      <c r="V4" s="255"/>
+      <c r="W4" s="256"/>
+      <c r="X4" s="254" t="s">
         <v>2</v>
       </c>
-      <c r="Y4" s="242"/>
-      <c r="Z4" s="243"/>
-      <c r="AB4" s="273" t="s">
+      <c r="Y4" s="255"/>
+      <c r="Z4" s="256"/>
+      <c r="AB4" s="266" t="s">
         <v>111</v>
       </c>
-      <c r="AC4" s="247" t="str">
+      <c r="AC4" s="260" t="str">
         <f>D4</f>
         <v>Área de Ensaio</v>
       </c>
-      <c r="AD4" s="249" t="s">
+      <c r="AD4" s="243" t="s">
         <v>154</v>
       </c>
-      <c r="AE4" s="249" t="s">
+      <c r="AE4" s="243" t="s">
         <v>144</v>
       </c>
-      <c r="AF4" s="249" t="s">
+      <c r="AF4" s="243" t="s">
         <v>139</v>
       </c>
-      <c r="AG4" s="249" t="s">
+      <c r="AG4" s="243" t="s">
         <v>171</v>
       </c>
-      <c r="AH4" s="249" t="s">
+      <c r="AH4" s="243" t="s">
         <v>157</v>
       </c>
-      <c r="AI4" s="244" t="s">
+      <c r="AI4" s="257" t="s">
         <v>156</v>
       </c>
-      <c r="AJ4" s="268" t="s">
+      <c r="AJ4" s="270" t="s">
         <v>173</v>
       </c>
       <c r="AO4" s="118">
@@ -19933,7 +19933,7 @@
       </c>
     </row>
     <row r="5" spans="4:44" ht="53.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D5" s="240"/>
+      <c r="D5" s="253"/>
       <c r="E5" s="57">
         <v>1</v>
       </c>
@@ -20000,15 +20000,15 @@
       <c r="Z5" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="AB5" s="274"/>
-      <c r="AC5" s="272"/>
-      <c r="AD5" s="270"/>
-      <c r="AE5" s="270"/>
-      <c r="AF5" s="270"/>
-      <c r="AG5" s="270"/>
-      <c r="AH5" s="270"/>
-      <c r="AI5" s="271"/>
-      <c r="AJ5" s="269"/>
+      <c r="AB5" s="267"/>
+      <c r="AC5" s="274"/>
+      <c r="AD5" s="272"/>
+      <c r="AE5" s="272"/>
+      <c r="AF5" s="272"/>
+      <c r="AG5" s="272"/>
+      <c r="AH5" s="272"/>
+      <c r="AI5" s="273"/>
+      <c r="AJ5" s="271"/>
       <c r="AL5" t="s">
         <v>166</v>
       </c>
@@ -21617,10 +21617,10 @@
         <f>SUMPRODUCT(INDEX(Curvas!$B$3:$E$5,MATCH(AD18,Curvas!$A$3:$A$5,0),0),CHOOSE({1,2,3,4},AF18^3,AF18^2,AF18,1))</f>
         <v>23.033980262940187</v>
       </c>
-      <c r="AP18" s="256" t="s">
+      <c r="AP18" s="244" t="s">
         <v>133</v>
       </c>
-      <c r="AQ18" s="257">
+      <c r="AQ18" s="245">
         <v>80</v>
       </c>
     </row>
@@ -21737,8 +21737,8 @@
         <f>SUMPRODUCT(INDEX(Curvas!$B$3:$E$5,MATCH(AD19,Curvas!$A$3:$A$5,0),0),CHOOSE({1,2,3,4},AF19^3,AF19^2,AF19,1))</f>
         <v>24.07937518241447</v>
       </c>
-      <c r="AP19" s="256"/>
-      <c r="AQ19" s="257"/>
+      <c r="AP19" s="244"/>
+      <c r="AQ19" s="245"/>
     </row>
     <row r="20" spans="4:56" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D20" s="11" t="s">
@@ -22659,10 +22659,10 @@
         <f t="shared" si="2"/>
         <v>25.684567670980822</v>
       </c>
-      <c r="BC27" s="250" t="s">
+      <c r="BC27" s="241" t="s">
         <v>171</v>
       </c>
-      <c r="BD27" s="250" t="s">
+      <c r="BD27" s="241" t="s">
         <v>157</v>
       </c>
     </row>
@@ -22762,8 +22762,8 @@
       </c>
       <c r="AI28" s="131"/>
       <c r="AJ28" s="154"/>
-      <c r="BC28" s="250"/>
-      <c r="BD28" s="250"/>
+      <c r="BC28" s="241"/>
+      <c r="BD28" s="241"/>
     </row>
     <row r="29" spans="4:56" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D29" s="11" t="s">
@@ -22864,7 +22864,7 @@
       <c r="AL29" s="116"/>
       <c r="AM29" s="116"/>
       <c r="AN29" s="116"/>
-      <c r="AO29" s="262"/>
+      <c r="AO29" s="250"/>
       <c r="BC29" s="19"/>
       <c r="BD29" s="19"/>
     </row>
@@ -22967,7 +22967,7 @@
       <c r="AL30" s="116"/>
       <c r="AM30" s="116"/>
       <c r="AN30" s="116"/>
-      <c r="AO30" s="262"/>
+      <c r="AO30" s="250"/>
       <c r="BC30" s="19"/>
       <c r="BD30" s="19"/>
     </row>
@@ -23070,7 +23070,7 @@
       <c r="AL31" s="117"/>
       <c r="AM31" s="117"/>
       <c r="AN31" s="117"/>
-      <c r="AO31" s="263"/>
+      <c r="AO31" s="251"/>
       <c r="BC31" s="19"/>
       <c r="BD31" s="19"/>
     </row>
@@ -24281,10 +24281,10 @@
       <c r="S44" s="34"/>
       <c r="T44" s="34"/>
       <c r="AB44" s="35"/>
-      <c r="AC44" s="258" t="s">
+      <c r="AC44" s="246" t="s">
         <v>167</v>
       </c>
-      <c r="AD44" s="259"/>
+      <c r="AD44" s="247"/>
       <c r="AE44" s="135">
         <f t="shared" ref="AE44:AJ44" si="13">AVERAGE(AE6:AE27)</f>
         <v>34.332315601065609</v>
@@ -24338,10 +24338,10 @@
       <c r="S45" s="34"/>
       <c r="T45" s="34"/>
       <c r="AB45" s="35"/>
-      <c r="AC45" s="260" t="s">
+      <c r="AC45" s="248" t="s">
         <v>168</v>
       </c>
-      <c r="AD45" s="261"/>
+      <c r="AD45" s="249"/>
       <c r="AE45" s="126">
         <f>MEDIAN(AE6:AE27)</f>
         <v>33.589285714285715</v>
@@ -24384,10 +24384,10 @@
       <c r="I46" s="19"/>
       <c r="J46" s="19"/>
       <c r="K46" s="21"/>
-      <c r="AC46" s="260" t="s">
+      <c r="AC46" s="248" t="s">
         <v>169</v>
       </c>
-      <c r="AD46" s="261"/>
+      <c r="AD46" s="249"/>
       <c r="AE46" s="126">
         <f>_xlfn.STDEV.S(AE6:AE27)</f>
         <v>3.1767550066302315</v>
@@ -24430,10 +24430,10 @@
       <c r="I47" s="19"/>
       <c r="J47" s="19"/>
       <c r="K47" s="21"/>
-      <c r="AC47" s="266" t="s">
+      <c r="AC47" s="268" t="s">
         <v>170</v>
       </c>
-      <c r="AD47" s="267"/>
+      <c r="AD47" s="269"/>
       <c r="AE47" s="139">
         <f>AE46/AE44</f>
         <v>9.2529587678951405E-2</v>
@@ -24581,16 +24581,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:T4"/>
-    <mergeCell ref="U4:W4"/>
-    <mergeCell ref="X4:Z4"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="AP18:AP19"/>
-    <mergeCell ref="AQ18:AQ19"/>
-    <mergeCell ref="BC27:BC28"/>
-    <mergeCell ref="BD27:BD28"/>
-    <mergeCell ref="AO29:AO31"/>
     <mergeCell ref="AC44:AD44"/>
     <mergeCell ref="AC45:AD45"/>
     <mergeCell ref="AC46:AD46"/>
@@ -24603,6 +24593,16 @@
     <mergeCell ref="AH4:AH5"/>
     <mergeCell ref="AI4:AI5"/>
     <mergeCell ref="AC4:AC5"/>
+    <mergeCell ref="AP18:AP19"/>
+    <mergeCell ref="AQ18:AQ19"/>
+    <mergeCell ref="BC27:BC28"/>
+    <mergeCell ref="BD27:BD28"/>
+    <mergeCell ref="AO29:AO31"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:T4"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X4:Z4"/>
+    <mergeCell ref="AB4:AB5"/>
   </mergeCells>
   <conditionalFormatting sqref="D44:F44 L45:T45">
     <cfRule type="cellIs" dxfId="7" priority="14" operator="greaterThan">
